--- a/data/trans_camb/IP15-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IP15-Dificultad-trans_camb.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -66,13 +66,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -513,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,9 +517,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,68 +532,50 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niña</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
     </row>
@@ -616,9 +588,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -631,15 +600,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n">
+        <v>-7.606670280146465</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-0.3943579802908964</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.3451679584657669</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-3.404712430035264</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>-3.805511920104721</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-1.756634523586903</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -648,15 +626,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>-13.23024266808651</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-7.986453733765019</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-6.588052039720687</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-12.48609488030969</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-8.202156271355038</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-8.409036491127367</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -665,15 +652,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>-1.645783664430288</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>8.607978505891825</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>6.351831441697469</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>7.701120295041792</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0.5965287017657558</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>4.76896285620101</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -682,15 +678,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>-0.3081027645509321</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>-0.01597318925042294</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>0.01494807234559115</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.1474467327335893</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.1591567951033603</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.07346720410070771</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -699,15 +704,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="n">
+        <v>-0.4786512446586373</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>-0.3014833123662588</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-0.2495303525329033</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.4953195675384119</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.3129991784225277</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.3246303758189825</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -716,15 +730,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="n">
+        <v>-0.07264827146460881</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.3931855318211969</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0.319106608995286</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0.3696969153267771</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.02027861339694508</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.2122858978108831</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -737,15 +760,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>-4.499685874439685</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>2.972734039594713</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-1.922950074107121</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>5.56369898359437</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>-3.213765987102307</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>4.209118163745382</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -754,15 +786,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>-10.99915198306084</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-4.571307761345408</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-7.622535927740823</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-0.7029205882129592</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-7.498924527549327</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-0.7520800465819205</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -771,15 +812,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>1.427858873139416</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>10.96659695809507</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>4.530641432563258</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>12.13334658396581</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>1.25819997995598</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>9.689624652448497</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,15 +838,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>-0.2257708484616498</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0.149156342264381</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-0.09899560997771312</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0.2864254158387602</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.1633263032605699</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.2139109420008827</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -805,15 +864,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="n">
+        <v>-0.4720841637202572</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-0.2027577202402449</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-0.3535821374017233</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.04446993991076315</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.3455142594330719</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.03558986088992324</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -822,15 +890,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
+      <c r="C15" s="6" t="n">
+        <v>0.09499503508650417</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>0.6366168103485337</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>0.280330395791325</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.7414184194498323</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.07614002586508212</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.5500441581978315</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -843,15 +920,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>-1.833582095336855</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>4.19161990633482</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-6.429249235164026</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>2.876202917096374</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>-4.209529799060166</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>3.665827812399064</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -860,15 +946,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>-8.935930198013384</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-2.626451371666273</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-12.88938613673095</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-4.193836011444712</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-8.694430524947656</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-1.640811616970162</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -877,15 +972,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>6.228404190003774</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>11.45197076823905</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.5419639950055298</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>10.03944605655035</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0.8984739833671608</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>8.362647044824469</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -894,15 +998,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="n">
+        <v>-0.09483774052096333</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>0.2168017249134708</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-0.362961779984744</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>0.1623753710894954</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.2270934849192913</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>0.1977621379987924</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -911,15 +1024,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr"/>
-      <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
+      <c r="C20" s="6" t="n">
+        <v>-0.3929614877989834</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-0.1139060750259065</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-0.6211496711965228</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-0.1975041668790258</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.4170618737783616</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.0811862807951514</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -928,15 +1050,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
+      <c r="C21" s="6" t="n">
+        <v>0.3694640404656697</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>0.7171341796125359</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>0.03752786294698261</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>0.7172781862610856</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.05764422556896472</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.5334391095318932</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -949,15 +1080,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>-1.567029351570165</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>5.978197446827233</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-9.492690937156883</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-1.557507853789841</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-5.141341485180234</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>2.502124626249622</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -966,15 +1106,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>-9.411012593776469</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-2.257860882632824</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-19.44973631115775</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-11.95239199820902</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-12.19685686853204</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-4.94960245449295</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -983,15 +1132,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n">
+        <v>7.236380999035467</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>15.10783492608995</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>1.342544536285517</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>7.650609349070603</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>1.793167965361089</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>8.672969402158733</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1000,15 +1158,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="n">
+        <v>-0.08496051353187199</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>0.3241233002869031</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>-0.3857551512579573</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-0.0632925565260323</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-0.2419977005342343</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>0.1177724544747415</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1017,15 +1184,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr"/>
-      <c r="D26" s="6" t="inlineStr"/>
-      <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr"/>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
+      <c r="C26" s="6" t="n">
+        <v>-0.4306951673116028</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>-0.1115722693762254</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>-0.6585546314742347</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-0.3778449017421762</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>-0.4917006420178942</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.1811083295396817</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1034,15 +1210,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr"/>
-      <c r="D27" s="6" t="inlineStr"/>
-      <c r="E27" s="6" t="inlineStr"/>
-      <c r="F27" s="6" t="inlineStr"/>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
+      <c r="C27" s="6" t="n">
+        <v>0.5349666881899852</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>1.119929556030884</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>0.08762678760164626</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>0.4120063081498758</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0.1084038258768319</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>0.5050657453371966</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1055,15 +1240,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>-4.570521181468523</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>2.375037551540815</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-2.8399494914255</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>1.49139334142295</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>-3.730266332964571</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>1.96828246884031</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1072,15 +1266,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>-7.447270072262267</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-1.64425560682332</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-6.465211513201162</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>-2.449829375018093</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-6.281285781586164</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>-0.9009550269789954</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1089,15 +1292,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>-1.055152773546371</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>6.070195943953316</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>0.3865941312087057</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>5.181268726976432</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>-1.293938990432926</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>4.583398869096218</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1106,15 +1318,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="n">
+        <v>-0.2149691050058629</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>0.1117071065943513</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>-0.1357927716258629</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>0.07131128072088529</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>-0.1768604187701536</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>0.09332075262851085</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1123,15 +1344,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="n">
+        <v>-0.3358974366358292</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>-0.07319771722692384</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>-0.2832373654644476</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>-0.1117579868527765</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>-0.2767682478446291</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>-0.0449263300125617</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1140,15 +1370,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="C33" s="6" t="n">
+        <v>-0.05504530822748133</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>0.311135745112383</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>0.02574872852464972</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>0.2678651420767271</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>-0.06508638343492451</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>0.234256654373805</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1159,11 +1398,11 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
